--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/3mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/3mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.62904789352</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>540.611388900671</v>
       </c>
-      <c r="W2" t="b">
+      <c r="V2" t="b">
         <v>0</v>
       </c>
+      <c r="W2" t="s">
+        <v>29</v>
+      </c>
       <c r="X2">
-        <v>544.391323550034</v>
+        <v>0.25327007</v>
+      </c>
+      <c r="Y2">
+        <v>0.262972586</v>
+      </c>
+      <c r="Z2">
+        <v>0.3651031489118278</v>
+      </c>
+      <c r="AA2">
+        <v>4.851258000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.07592094018640907</v>
+      </c>
+      <c r="AC2">
+        <v>41.04372492081938</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.62916363426</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>539.4948413046868</v>
       </c>
-      <c r="W3" t="b">
+      <c r="V3" t="b">
         <v>0</v>
       </c>
+      <c r="W3">
+        <v>543.8989877762394</v>
+      </c>
+      <c r="X3">
+        <v>0.253232238</v>
+      </c>
+      <c r="Y3">
+        <v>0.262956032</v>
+      </c>
+      <c r="Z3">
+        <v>0.3650649820616512</v>
+      </c>
+      <c r="AA3">
+        <v>4.861896999999999</v>
+      </c>
+      <c r="AB3">
+        <v>0.07574991077786572</v>
+      </c>
+      <c r="AC3">
+        <v>40.86668609394885</v>
+      </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.6292799537</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>539.3554590847565</v>
       </c>
-      <c r="V4">
-        <v>0.688411897029915</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.253202672</v>
+      </c>
+      <c r="Y4">
+        <v>0.262937248</v>
+      </c>
+      <c r="Z4">
+        <v>0.3650309432003718</v>
+      </c>
+      <c r="AA4">
+        <v>4.867287999999995</v>
+      </c>
+      <c r="AB4">
+        <v>0.075660541230941</v>
+      </c>
+      <c r="AC4">
+        <v>40.80792595021533</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.62939627315</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>541.6589337912892</v>
       </c>
-      <c r="V5">
-        <v>1.291557162074619</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>40.90662323189761</v>
+      </c>
+      <c r="X5">
+        <v>0.253182008</v>
+      </c>
+      <c r="Y5">
+        <v>0.262918146</v>
+      </c>
+      <c r="Z5">
+        <v>0.3650028502231036</v>
+      </c>
+      <c r="AA5">
+        <v>4.868068999999998</v>
+      </c>
+      <c r="AB5">
+        <v>0.07564289460670216</v>
+      </c>
+      <c r="AC5">
+        <v>40.97264964155315</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.62951259259</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>542.6150659955553</v>
       </c>
-      <c r="V6">
-        <v>1.675570635564543</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.253145132</v>
+      </c>
+      <c r="Y6">
+        <v>0.2629</v>
+      </c>
+      <c r="Z6">
+        <v>0.3649642007859092</v>
+      </c>
+      <c r="AA6">
+        <v>4.877434000000001</v>
+      </c>
+      <c r="AB6">
+        <v>0.07549234159984895</v>
+      </c>
+      <c r="AC6">
+        <v>40.96328191936104</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.62962833334</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>541.8647267528225</v>
       </c>
-      <c r="V7">
-        <v>0.5032475391949761</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.253129872</v>
+      </c>
+      <c r="Y7">
+        <v>0.262889494</v>
+      </c>
+      <c r="Z7">
+        <v>0.3649460482788003</v>
+      </c>
+      <c r="AA7">
+        <v>4.879810999999997</v>
+      </c>
+      <c r="AB7">
+        <v>0.07545252688957566</v>
+      </c>
+      <c r="AC7">
+        <v>40.88506286582991</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.62974465278</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>543.2784843899831</v>
       </c>
-      <c r="V8">
-        <v>0.7073240183816795</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.253107936</v>
+      </c>
+      <c r="Y8">
+        <v>0.26287676</v>
+      </c>
+      <c r="Z8">
+        <v>0.3649216603797008</v>
+      </c>
+      <c r="AA8">
+        <v>4.884412000000005</v>
+      </c>
+      <c r="AB8">
+        <v>0.07537775254116409</v>
+      </c>
+      <c r="AC8">
+        <v>40.95111115728682</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.62986039352</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>544.1048461898461</v>
       </c>
-      <c r="V9">
-        <v>1.132822402455518</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.253090452</v>
+      </c>
+      <c r="Y9">
+        <v>0.262868482</v>
+      </c>
+      <c r="Z9">
+        <v>0.364903570443684</v>
+      </c>
+      <c r="AA9">
+        <v>4.889015000000001</v>
+      </c>
+      <c r="AB9">
+        <v>0.07530436677243257</v>
+      </c>
+      <c r="AC9">
+        <v>40.97347090013818</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.62997671296</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>543.6190589831446</v>
       </c>
-      <c r="V10">
-        <v>0.4153019158739552</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.253082822</v>
+      </c>
+      <c r="Y10">
+        <v>0.262865298</v>
+      </c>
+      <c r="Z10">
+        <v>0.3648959847464925</v>
+      </c>
+      <c r="AA10">
+        <v>4.891238000000001</v>
+      </c>
+      <c r="AB10">
+        <v>0.07526920851974336</v>
+      </c>
+      <c r="AC10">
+        <v>40.91777630590897</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.63009303241</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>544.1500499466566</v>
       </c>
-      <c r="V11">
-        <v>0.2943874977962839</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.253064066</v>
+      </c>
+      <c r="Y11">
+        <v>0.26286307</v>
+      </c>
+      <c r="Z11">
+        <v>0.3648813712294411</v>
+      </c>
+      <c r="AA11">
+        <v>4.899501999999998</v>
+      </c>
+      <c r="AB11">
+        <v>0.07514153842061677</v>
+      </c>
+      <c r="AC11">
+        <v>40.88827188464723</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.63020935185</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>543.7751136293679</v>
       </c>
-      <c r="V12">
-        <v>0.2729107601268242</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.25306343</v>
+      </c>
+      <c r="Y12">
+        <v>0.26286116</v>
+      </c>
+      <c r="Z12">
+        <v>0.3648795541543955</v>
+      </c>
+      <c r="AA12">
+        <v>4.898865000000001</v>
+      </c>
+      <c r="AB12">
+        <v>0.07515076842886499</v>
+      </c>
+      <c r="AC12">
+        <v>40.86511764174037</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.63032509259</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>546.2118197532494</v>
       </c>
-      <c r="V13">
-        <v>1.31206000317295</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.253051986</v>
+      </c>
+      <c r="Y13">
+        <v>0.262861796</v>
+      </c>
+      <c r="Z13">
+        <v>0.3648720754112184</v>
+      </c>
+      <c r="AA13">
+        <v>4.904904999999999</v>
+      </c>
+      <c r="AB13">
+        <v>0.07505835467757042</v>
+      </c>
+      <c r="AC13">
+        <v>40.99776049612056</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.63044141204</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>544.21842972558</v>
       </c>
-      <c r="V14">
-        <v>1.297925890137154</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
+      <c r="X14">
+        <v>0.253049444</v>
+      </c>
+      <c r="Y14">
+        <v>0.262863706</v>
+      </c>
+      <c r="Z14">
+        <v>0.3648716884615241</v>
+      </c>
+      <c r="AA14">
+        <v>4.907131</v>
+      </c>
+      <c r="AB14">
+        <v>0.07502483263770394</v>
+      </c>
+      <c r="AC14">
+        <v>40.82989660851568</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.63055773148</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>543.4435268288505</v>
       </c>
-      <c r="V15">
-        <v>1.428141217167984</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.253050078</v>
+      </c>
+      <c r="Y15">
+        <v>0.262862434</v>
+      </c>
+      <c r="Z15">
+        <v>0.3648712117778141</v>
+      </c>
+      <c r="AA15">
+        <v>4.906177999999997</v>
+      </c>
+      <c r="AB15">
+        <v>0.07503905065192971</v>
+      </c>
+      <c r="AC15">
+        <v>40.77948633617344</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.63067347222</v>
       </c>
@@ -1553,11 +1814,26 @@
       <c r="U16">
         <v>545.6077433435772</v>
       </c>
-      <c r="V16">
-        <v>1.096547608870954</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
+      </c>
+      <c r="X16">
+        <v>0.253042768</v>
+      </c>
+      <c r="Y16">
+        <v>0.262859886</v>
+      </c>
+      <c r="Z16">
+        <v>0.3648643064277935</v>
+      </c>
+      <c r="AA16">
+        <v>4.908559000000004</v>
+      </c>
+      <c r="AB16">
+        <v>0.07500190372001853</v>
+      </c>
+      <c r="AC16">
+        <v>40.92161943515156</v>
       </c>
     </row>
   </sheetData>
